--- a/artfynd/A 27011-2026 artfynd.xlsx
+++ b/artfynd/A 27011-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150781</v>
+        <v>121150778</v>
       </c>
       <c r="B2" t="n">
-        <v>91989</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>760000</v>
+        <v>759957</v>
       </c>
       <c r="R2" t="n">
-        <v>7413403</v>
+        <v>7413436</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,19 +781,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150778</v>
+        <v>121150781</v>
       </c>
       <c r="B3" t="n">
-        <v>91989</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -821,7 +811,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,13 +820,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759957</v>
+        <v>760000</v>
       </c>
       <c r="R3" t="n">
-        <v>7413436</v>
+        <v>7413403</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,19 +887,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150782</v>
+        <v>121150777</v>
       </c>
       <c r="B4" t="n">
-        <v>92001</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -932,7 +917,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760023</v>
+        <v>760029</v>
       </c>
       <c r="R4" t="n">
-        <v>7413355</v>
+        <v>7413670</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,19 +993,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150777</v>
+        <v>121150782</v>
       </c>
       <c r="B5" t="n">
-        <v>92001</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1043,7 +1023,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760029</v>
+        <v>760023</v>
       </c>
       <c r="R5" t="n">
-        <v>7413670</v>
+        <v>7413355</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,38 +1099,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150779</v>
+        <v>121150786</v>
       </c>
       <c r="B6" t="n">
-        <v>97059</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224358</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1159,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>759963</v>
+        <v>759960</v>
       </c>
       <c r="R6" t="n">
-        <v>7413434</v>
+        <v>7413328</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1223,6 +1202,108 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121150779</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97990</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>224358</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig plattlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum subsp. complanatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nattavaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>759963</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7413434</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
